--- a/docs/StructureDefinition-bfrt-activity-definition.xlsx
+++ b/docs/StructureDefinition-bfrt-activity-definition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-bfrt-activity-definition.xlsx
+++ b/docs/StructureDefinition-bfrt-activity-definition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="472">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/bfrt-activity-definition</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/bfrt-activity-definition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -449,7 +452,7 @@
     <t>sexSpecificProtocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/sex-specific-protocol}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/sex-specific-protocol}
 </t>
   </si>
   <si>
@@ -1102,7 +1105,7 @@
     <t>Allows matching performed to planned as well as validation against protocols.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/bfrt-protocol-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/bfrt-protocol-vs</t>
   </si>
   <si>
     <t>.code</t>
@@ -1739,54 +1742,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1814,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.46875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1824,7 +1829,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="77.76953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.44140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1842,132 +1847,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1975,10 +1980,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1990,13 +1995,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2047,25 +2052,25 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>20</v>
@@ -2076,10 +2081,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2087,10 +2092,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2099,19 +2104,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2161,13 +2166,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2190,10 +2195,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2201,10 +2206,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2213,16 +2218,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2273,19 +2278,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2302,10 +2307,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2313,31 +2318,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2387,19 +2392,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2416,10 +2421,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2427,10 +2432,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2442,16 +2447,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2477,13 +2482,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2501,19 +2506,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2530,21 +2535,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2556,16 +2561,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2615,25 +2620,25 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -2644,21 +2649,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2670,16 +2675,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2729,13 +2734,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2747,7 +2752,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2758,10 +2763,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2769,10 +2774,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2784,13 +2789,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2829,29 +2834,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2868,26 +2873,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2896,13 +2901,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2953,19 +2958,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2982,45 +2987,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3069,25 +3074,25 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -3098,10 +3103,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3109,10 +3114,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3121,22 +3126,22 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3185,28 +3190,28 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>20</v>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3225,10 +3230,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3237,22 +3242,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3301,39 +3306,39 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>157</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3341,10 +3346,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3353,19 +3358,19 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3415,28 +3420,28 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3444,10 +3449,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3455,34 +3460,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3531,25 +3536,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -3560,10 +3565,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3571,31 +3576,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3645,25 +3650,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3674,10 +3679,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3685,10 +3690,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3700,13 +3705,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3757,19 +3762,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3786,10 +3791,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3797,31 +3802,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3847,13 +3852,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3871,28 +3876,28 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3900,10 +3905,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3911,10 +3916,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3923,22 +3928,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3987,28 +3992,28 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -4016,10 +4021,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4027,10 +4032,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4042,13 +4047,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4056,7 +4061,7 @@
         <v>20</v>
       </c>
       <c r="Q20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>20</v>
@@ -4077,13 +4082,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4101,22 +4106,22 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
@@ -4130,21 +4135,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4153,19 +4158,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4215,28 +4220,28 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4244,10 +4249,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4255,10 +4260,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4267,22 +4272,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4331,28 +4336,28 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4360,10 +4365,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4371,10 +4376,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4383,19 +4388,19 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4445,25 +4450,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4474,10 +4479,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4485,31 +4490,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4559,25 +4564,25 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4588,10 +4593,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4599,10 +4604,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4611,22 +4616,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4675,25 +4680,25 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4704,10 +4709,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4715,10 +4720,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4727,19 +4732,19 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4765,13 +4770,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4789,25 +4794,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4818,10 +4823,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4829,10 +4834,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4844,16 +4849,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4903,39 +4908,39 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4943,10 +4948,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4958,13 +4963,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5015,25 +5020,25 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5044,21 +5049,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5070,17 +5075,17 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5129,39 +5134,39 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5169,10 +5174,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5184,16 +5189,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5243,39 +5248,39 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5283,10 +5288,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5298,19 +5303,19 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5359,39 +5364,39 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5399,10 +5404,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5411,22 +5416,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5475,39 +5480,39 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5515,10 +5520,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5530,17 +5535,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5565,13 +5570,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5589,25 +5594,25 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5618,10 +5623,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5629,10 +5634,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5644,13 +5649,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5701,25 +5706,25 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5730,10 +5735,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5741,10 +5746,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5756,13 +5761,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5813,19 +5818,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5842,10 +5847,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5853,10 +5858,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5868,13 +5873,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5925,25 +5930,25 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -5954,10 +5959,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5965,10 +5970,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5980,13 +5985,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6037,25 +6042,25 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -6066,10 +6071,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6077,10 +6082,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6092,19 +6097,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6153,25 +6158,25 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
@@ -6182,10 +6187,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6193,10 +6198,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6208,13 +6213,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6265,25 +6270,25 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6294,10 +6299,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6305,10 +6310,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6317,19 +6322,19 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6355,13 +6360,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6379,25 +6384,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6408,10 +6413,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6419,10 +6424,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6434,17 +6439,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6493,19 +6498,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6522,10 +6527,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6533,34 +6538,34 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6585,11 +6590,11 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6607,25 +6612,25 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6636,10 +6641,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6647,10 +6652,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6662,13 +6667,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6695,13 +6700,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6719,19 +6724,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6748,10 +6753,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6759,10 +6764,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6774,13 +6779,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6807,13 +6812,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6831,19 +6836,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -6860,10 +6865,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6871,31 +6876,31 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6945,19 +6950,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -6974,10 +6979,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6985,10 +6990,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7000,17 +7005,17 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7059,25 +7064,25 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7088,21 +7093,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7114,19 +7119,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7175,25 +7180,25 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7204,10 +7209,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7215,10 +7220,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7230,13 +7235,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7287,25 +7292,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7316,10 +7321,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7327,10 +7332,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7342,13 +7347,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7399,13 +7404,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7417,7 +7422,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7428,21 +7433,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7454,16 +7459,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7513,25 +7518,25 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7542,45 +7547,45 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7629,25 +7634,25 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7658,10 +7663,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7669,10 +7674,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7684,13 +7689,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7717,13 +7722,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7741,25 +7746,25 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7770,10 +7775,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7781,10 +7786,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7796,13 +7801,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7829,13 +7834,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -7853,25 +7858,25 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -7882,10 +7887,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7893,10 +7898,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7908,13 +7913,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7941,13 +7946,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7965,25 +7970,25 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -7994,21 +7999,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8020,13 +8025,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8077,25 +8082,25 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8106,10 +8111,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8117,13 +8122,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -8132,16 +8137,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8191,25 +8196,25 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8220,10 +8225,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8231,10 +8236,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8246,19 +8251,19 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8283,13 +8288,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8307,25 +8312,25 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8336,10 +8341,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8347,10 +8352,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8362,17 +8367,17 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8421,19 +8426,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8450,10 +8455,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8461,10 +8466,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8476,17 +8481,17 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8535,19 +8540,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -8564,10 +8569,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8575,10 +8580,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8590,13 +8595,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8647,19 +8652,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -8676,10 +8681,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8687,10 +8692,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8702,16 +8707,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8761,25 +8766,25 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -8790,10 +8795,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8801,10 +8806,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8816,16 +8821,16 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8875,25 +8880,25 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
@@ -8904,10 +8909,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8915,10 +8920,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8930,13 +8935,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8987,13 +8992,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9005,7 +9010,7 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
@@ -9016,21 +9021,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9042,16 +9047,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9101,25 +9106,25 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
@@ -9130,45 +9135,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9217,25 +9222,25 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
@@ -9246,10 +9251,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9257,10 +9262,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9272,16 +9277,16 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9331,25 +9336,25 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9360,10 +9365,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9371,10 +9376,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9386,16 +9391,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9445,25 +9450,25 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
